--- a/artfynd/A 21309-2023 artfynd.xlsx
+++ b/artfynd/A 21309-2023 artfynd.xlsx
@@ -904,7 +904,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elvira Ljungberg, Noah Wester</t>
+          <t>Noah Wester, Elvira Ljungberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elvira Ljungberg, Noah Wester</t>
+          <t>Noah Wester, Elvira Ljungberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 21309-2023 artfynd.xlsx
+++ b/artfynd/A 21309-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136438295</v>
       </c>
       <c r="B2" t="n">
-        <v>108105</v>
+        <v>108108</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136438298</v>
       </c>
       <c r="B3" t="n">
-        <v>108105</v>
+        <v>108108</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136438300</v>
       </c>
       <c r="B4" t="n">
-        <v>108105</v>
+        <v>108108</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21309-2023 artfynd.xlsx
+++ b/artfynd/A 21309-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136438295</v>
       </c>
       <c r="B2" t="n">
-        <v>108108</v>
+        <v>108109</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136438298</v>
       </c>
       <c r="B3" t="n">
-        <v>108108</v>
+        <v>108109</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136438300</v>
       </c>
       <c r="B4" t="n">
-        <v>108108</v>
+        <v>108109</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21309-2023 artfynd.xlsx
+++ b/artfynd/A 21309-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136438295</v>
       </c>
       <c r="B2" t="n">
-        <v>108109</v>
+        <v>108114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136438298</v>
       </c>
       <c r="B3" t="n">
-        <v>108109</v>
+        <v>108114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136438300</v>
       </c>
       <c r="B4" t="n">
-        <v>108109</v>
+        <v>108114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21309-2023 artfynd.xlsx
+++ b/artfynd/A 21309-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136438295</v>
       </c>
       <c r="B2" t="n">
-        <v>108114</v>
+        <v>108116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136438298</v>
       </c>
       <c r="B3" t="n">
-        <v>108114</v>
+        <v>108116</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136438300</v>
       </c>
       <c r="B4" t="n">
-        <v>108114</v>
+        <v>108116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21309-2023 artfynd.xlsx
+++ b/artfynd/A 21309-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136438295</v>
       </c>
       <c r="B2" t="n">
-        <v>108116</v>
+        <v>108122</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136438298</v>
       </c>
       <c r="B3" t="n">
-        <v>108116</v>
+        <v>108122</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136438300</v>
       </c>
       <c r="B4" t="n">
-        <v>108116</v>
+        <v>108122</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21309-2023 artfynd.xlsx
+++ b/artfynd/A 21309-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136438295</v>
       </c>
       <c r="B2" t="n">
-        <v>108122</v>
+        <v>108124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136438298</v>
       </c>
       <c r="B3" t="n">
-        <v>108122</v>
+        <v>108124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136438300</v>
       </c>
       <c r="B4" t="n">
-        <v>108122</v>
+        <v>108124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21309-2023 artfynd.xlsx
+++ b/artfynd/A 21309-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136438295</v>
       </c>
       <c r="B2" t="n">
-        <v>108124</v>
+        <v>108125</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136438298</v>
       </c>
       <c r="B3" t="n">
-        <v>108124</v>
+        <v>108125</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>136438300</v>
       </c>
       <c r="B4" t="n">
-        <v>108124</v>
+        <v>108125</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
